--- a/event_registration_forms/012_field_trip_preparation_checklist_form--event_registration_forms.xlsx
+++ b/event_registration_forms/012_field_trip_preparation_checklist_form--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_1</t>
+          <t>school_approval</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -538,24 +538,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>school_approval</t>
+          <t>safety_protocols</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>School Approval</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Get approval from the school administration</t>
-        </is>
-      </c>
+          <t>Safety Protocols</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -565,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_2</t>
+          <t>transportation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Safety Protocols</t>
+          <t>Transportation</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -588,24 +584,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>safety_protocols</t>
+          <t>accommodations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Safety Protocols</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Review and finalize safety protocols</t>
-        </is>
-      </c>
+          <t>Accommodations</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -615,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_3</t>
+          <t>emergency_contact</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Transportation</t>
+          <t>Emergency Contact</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -638,24 +630,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>transportation</t>
+          <t>field_trip_permission</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Transportation</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Arrange for buses or other approved transportation</t>
-        </is>
-      </c>
+          <t>Field Trip Permission</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -665,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_4</t>
+          <t>food_and_supplies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Accommodations</t>
+          <t>Food and Supplies</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -693,19 +681,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>accommodations</t>
+          <t>medical_care</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Accommodations</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Arrange for accommodations</t>
-        </is>
-      </c>
+          <t>Medical Care</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -720,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_5</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Emergency Contact</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -743,19 +727,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>emergency_contact</t>
+          <t>first_aid_kit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Emergency Contact</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Identify an emergency contact</t>
-        </is>
-      </c>
+          <t>First Aid Kit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -770,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_6</t>
+          <t>field_trips</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Field Trip Permission</t>
+          <t>Field Trips</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -793,19 +773,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>field_trip_permission</t>
+          <t>weather</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Field Trip Permission</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Review field trip permission</t>
-        </is>
-      </c>
+          <t>Weather</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -815,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_7</t>
+          <t>field_trip_review</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Food and Supplies</t>
+          <t>Field Trip Review</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -838,298 +814,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>food_and_supplies</t>
+          <t>additional_information</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Food and Supplies</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Arrange for food and supplies</t>
-        </is>
-      </c>
+          <t>Additional Information</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_8</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Medical Care</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>medical_care</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Medical Care</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Ensure adequate medical care is available</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_9</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>insurance</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Verify necessary insurance</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>First Aid Kit</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>first_aid_kit</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>First Aid Kit</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Ensure a first aid kit is available</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_11</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Field Trips</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>field_trips</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Field Trips</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Review field trips</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_12</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Weather</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>weather</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Weather</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Monitor weather</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_13</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Field Trips Review</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1146,11 +845,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1174,748 +873,374 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_1_choices</t>
+          <t>school_approval_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_1_choices</t>
+          <t>school_approval_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>school_approval_choices</t>
+          <t>transportation_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>school_approval_choices</t>
+          <t>transportation_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_3_choices</t>
+          <t>accommodations_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_3_choices</t>
+          <t>accommodations_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>transportation_choices</t>
+          <t>emergency_contact_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>transportation_choices</t>
+          <t>emergency_contact_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_4_choices</t>
+          <t>field_trip_permission_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_4_choices</t>
+          <t>field_trip_permission_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>accommodations_choices</t>
+          <t>food_and_supplies_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>accommodations_choices</t>
+          <t>food_and_supplies_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_5_choices</t>
+          <t>medical_care_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_5_choices</t>
+          <t>medical_care_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>emergency_contact_choices</t>
+          <t>insurance_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>emergency_contact_choices</t>
+          <t>insurance_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_6_choices</t>
+          <t>first_aid_kit_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_6_choices</t>
+          <t>first_aid_kit_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>field_trip_permission_choices</t>
+          <t>field_trips_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>field_trip_permission_choices</t>
+          <t>field_trips_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_7_choices</t>
+          <t>weather_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>field_trip_preparation_checklist_form_7_choices</t>
+          <t>weather_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>food_and_supplies_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>food_and_supplies_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_8_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_8_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>medical_care_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>medical_care_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_9_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_9_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>insurance_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>insurance_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_10_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_10_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>first_aid_kit_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>first_aid_kit_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_11_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_11_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>field_trips_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>field_trips_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_12_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>field_trip_preparation_checklist_form_12_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>weather_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>weather_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
